--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/embedded-architecture-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/embedded-architecture-easy.xlsx
@@ -460,7 +460,7 @@
         <v>Super Loop (Bare-metal) là kiến trúc cơ bản nhất của lập trình nhúng: `main()` -&gt; Khởi tạo ngoại vi -&gt; `while(1) { task1(); task2(); }`. Chương trình chạy tuần tự từ trên xuống dưới không có hệ điều hành.</v>
       </c>
       <c r="F2" t="str">
-        <v>Cấu trúc chương trình đơn giản gồm hàm khởi tạo chạy một lần và một vòng lặp vô hạn `while(1)` thực thi tuần tự các tác vụ — cấu trúc tuần tự while(1)</v>
+        <v>Cơ chế tự động reset lại chip khi nhiệt độ môi trường tăng lên quá cao — reset nhiệt độ</v>
       </c>
       <c r="G2" t="str">
         <v>Một đoạn mã nguồn code lập trình bị lỗi lặp vô hạn làm sập máy chủ nạp chương trình — lỗi lặp mã nguồn</v>
@@ -469,10 +469,10 @@
         <v>Vòng dây bus vật lý nối các vi điều khiển lại với nhau để truyền dữ liệu chéo — vòng dây bus vật lý</v>
       </c>
       <c r="I2" t="str">
-        <v>Cơ chế tự động reset lại chip khi nhiệt độ môi trường tăng lên quá cao — reset nhiệt độ</v>
+        <v>Cấu trúc chương trình đơn giản gồm hàm khởi tạo chạy một lần và một vòng lặp vô hạn `while(1)` thực thi tuần tự các tác vụ — cấu trúc tuần tự while(1)</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Phân tầng giúp code nhúng độc lập với phần cứng. Ví dụ: Tầng Application gọi hàm `Led_On()`. Hàm này gọi tầng HAL `HAL_GPIO_WritePin()`. Khi đổi sang chip khác, ta chỉ cần viết lại tầng HAL mà không cần sửa code xử lý logic ở tầng Application.</v>
       </c>
       <c r="F3" t="str">
-        <v>Application Layer (Ứng dụng), Middleware/Driver Layer (Trình điều khiển), HAL (Phần cứng trừu tượng) — kiến trúc phân tầng chuẩn nhúng</v>
+        <v>UI Layer, Controller Layer, Network Layer — kiến trúc ứng dụng di động</v>
       </c>
       <c r="G3" t="str">
         <v>Frontend Layer, Backend Layer, Database Layer — kiến trúc phân tầng web chuẩn</v>
       </c>
       <c r="H3" t="str">
-        <v>UI Layer, Controller Layer, Network Layer — kiến trúc ứng dụng di động</v>
+        <v>Application Layer (Ứng dụng), Middleware/Driver Layer (Trình điều khiển), HAL (Phần cứng trừu tượng) — kiến trúc phân tầng chuẩn nhúng</v>
       </c>
       <c r="I3" t="str">
         <v>Security Layer, Compiler Layer, Operating System Layer — kiến trúc bảo mật máy tính</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>FSM giúp thiết kế code điều khiển cực kỳ rõ ràng, tránh việc viết quá nhiều câu lệnh lồng nhau `if-else` phức tạp. Thường được triển khai bằng từ khóa `switch-case` kết hợp với `enum` trạng thái.</v>
       </c>
       <c r="F4" t="str">
+        <v>Tính toán chính xác số lượng bóng bán dẫn được tích hợp trong con chip vi điều khiển — cấu trúc transistor</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Tự động tối ưu hóa dung lượng của file chạy binary sau khi biên dịch xong — tối ưu dung lượng tệp nạp</v>
+      </c>
+      <c r="H4" t="str">
         <v>Quản lý các trạng thái hoạt động của hệ thống (ví dụ: Stop, Run, Error) và các điều kiện chuyển trạng thái rõ ràng — quản lý trạng thái hệ thống</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Tính toán chính xác số lượng bóng bán dẫn được tích hợp trong con chip vi điều khiển — cấu trúc transistor</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Tự động tối ưu hóa dung lượng của file chạy binary sau khi biên dịch xong — tối ưu dung lượng tệp nạp</v>
       </c>
       <c r="I4" t="str">
         <v>Đo lường điện áp tiêu thụ của toàn bộ bảng mạch điện tử khi chạy tải tối đa — đo điện áp mạch</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Watchdog Timer giống như một quả bom hẹn giờ. Chương trình hoạt động bình thường phải liên tục reset bộ đếm này (gọi là "clear watchdog" hoặc "feed the dog"). Nếu code bị treo ở vòng lặp vô hạn, watchdog không được feed sẽ đếm tràn và kích hoạt ngắt reset lại vi điều khiển.</v>
       </c>
       <c r="F5" t="str">
+        <v>Đo lường thời gian trôi qua và hiển thị giờ, phút, giây lên màn hình led — bộ hiển thị đồng hồ thời gian</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Tự động mã hóa toàn bộ dữ liệu lưu trong bộ nhớ Flash của vi điều khiển — mã hóa dữ liệu Flash</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Kết nối mạng không dây Wi-Fi để truyền dữ liệu về máy chủ giám sát — kết nối Wi-Fi</v>
+      </c>
+      <c r="I5" t="str">
         <v>Giám sát hoạt động của chương trình và tự động reset lại chip nếu hệ thống bị treo hoặc chạy sai luồng — giám sát reset hệ thống khi treo</v>
       </c>
-      <c r="G5" t="str">
-        <v>Đo lường thời gian trôi qua và hiển thị giờ, phút, giây lên màn hình led — bộ hiển thị đồng hồ thời gian</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Tự động mã hóa toàn bộ dữ liệu lưu trong bộ nhớ Flash của vi điều khiển — mã hóa dữ liệu Flash</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Kết nối mạng không dây Wi-Fi để truyền dữ liệu về máy chủ giám sát — kết nối Wi-Fi</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Bare-metal programming là viết code chạy trực tiếp trên vi điều khiển (thường dùng kiến trúc Super Loop hoặc Interrupt-driven), thích hợp cho các dòng chip nhỏ, yêu cầu tài nguyên RAM/Flash cực thấp.</v>
       </c>
       <c r="F6" t="str">
+        <v>Chỉ viết code bằng ngôn ngữ lập trình Assembly thô sơ nhất — lập trình Assembly thô</v>
+      </c>
+      <c r="G6" t="str">
         <v>Lập trình trực tiếp tương tác với phần cứng vi điều khiển mà không sử dụng bất kỳ hệ điều hành (RTOS) nào — lập trình không hệ điều hành</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>Sử dụng các thanh kim loại vật lý để hàn bảo vệ vỏ ngoài của con chip vi điều khiển — bảo vệ kim loại vỏ chip</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Chỉ viết code bằng ngôn ngữ lập trình Assembly thô sơ nhất — lập trình Assembly thô</v>
       </c>
       <c r="I6" t="str">
         <v>Quá trình tẩy sạch lớp oxit đồng trên bề mặt bảng mạch in PCB trước khi hàn linh kiện — tẩy bảng mạch in PCB</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>HAL (Hardware Abstraction Layer) do nhà sản xuất chip cung cấp (ví dụ: STM32Cube HAL). Nó trừu tượng hóa phần cứng bằng cách cung cấp các hàm như `HAL_GPIO_TogglePin()`, giúp lập trình viên không cần nhớ địa chỉ thanh ghi cụ thể.</v>
       </c>
       <c r="F7" t="str">
+        <v>Tính toán chi phí nguyên vật liệu cần thiết để sản xuất ra bảng mạch điện tử — tính chi phí sản xuất</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Dịch mã nguồn ngôn ngữ C sang mã nguồn ngôn ngữ Python để chạy thử nghiệm — dịch dịch ngôn ngữ code</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Tự động quét và vá các lỗ hổng bảo mật của hệ điều hành thời gian thực — quét lỗ hổng bảo mật</v>
+      </c>
+      <c r="I7" t="str">
         <v>Cung cấp các hàm API chuẩn hóa để tương tác với ngoại vi phần cứng, giúp che giấu cấu trúc thanh ghi phức tạp của chip — trừu tượng hóa phần cứng</v>
       </c>
-      <c r="G7" t="str">
-        <v>Tự động quét và vá các lỗ hổng bảo mật của hệ điều hành thời gian thực — quét lỗ hổng bảo mật</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Tính toán chi phí nguyên vật liệu cần thiết để sản xuất ra bảng mạch điện tử — tính chi phí sản xuất</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Dịch mã nguồn ngôn ngữ C sang mã nguồn ngôn ngữ Python để chạy thử nghiệm — dịch dịch ngôn ngữ code</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -687,13 +687,13 @@
         <v>Hệ thống ở chế độ ngủ (Sleep) rảnh rỗi và chỉ thức dậy xử lý công việc khi có sự kiện ngắt phần cứng xảy ra — xử lý dựa trên sự kiện ngắt</v>
       </c>
       <c r="G9" t="str">
+        <v>Toàn bộ mã nguồn chương trình được thực hiện hoàn toàn song song trên 100 con chip khác nhau — đa xử lý song song</v>
+      </c>
+      <c r="H9" t="str">
         <v>Lập trình viên liên tục gọi lệnh reset chip trong vòng lặp vô hạn while(1) — reset liên tục</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <v>Hệ thống bắt buộc phải gửi dữ liệu lên máy chủ internet cứ sau mỗi 5 giây — truyền dữ liệu định kỳ</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Toàn bộ mã nguồn chương trình được thực hiện hoàn toàn song song trên 100 con chip khác nhau — đa xử lý song song</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -716,19 +716,19 @@
         <v>Transition (chuyển trạng thái) là thành phần cấu tạo nên FSM (gồm States, Inputs/Events, Transitions, Actions).</v>
       </c>
       <c r="F10" t="str">
-        <v>Sự chuyển đổi từ trạng thái hiện tại sang một trạng thái khác khi thỏa mãn điều kiện kích hoạt cụ thể — chuyển đổi trạng thái</v>
+        <v>Quá trình biên dịch mã nguồn C nhúng sang file binary định dạng hex — biên dịch mã nguồn</v>
       </c>
       <c r="G10" t="str">
-        <v>Quá trình biên dịch mã nguồn C nhúng sang file binary định dạng hex — biên dịch mã nguồn</v>
+        <v>Hành động đo điện áp của các chân GPIO bằng máy đo dao động ký — đo điện áp chân GPIO</v>
       </c>
       <c r="H10" t="str">
         <v>Việc người dùng nhấn nút tắt nguồn điện cấp cho bảng mạch điện tử — ngắt nguồn điện</v>
       </c>
       <c r="I10" t="str">
-        <v>Hành động đo điện áp của các chân GPIO bằng máy đo dao động ký — đo điện áp chân GPIO</v>
+        <v>Sự chuyển đổi từ trạng thái hiện tại sang một trạng thái khác khi thỏa mãn điều kiện kích hoạt cụ thể — chuyển đổi trạng thái</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>SAD giúp tất cả các thành viên phát triển hiểu cấu trúc chung của dự án, cách phân lớp code, quản lý luồng dữ liệu và tích hợp ngoại vi nhất quán.</v>
       </c>
       <c r="F11" t="str">
+        <v>Liệt kê chi tiết giá bán của các linh kiện điện tử trên thị trường — danh sách giá linh kiện</v>
+      </c>
+      <c r="G11" t="str">
         <v>Mô tả cấu trúc tổng thể, sơ đồ khối, phân tầng, giao tiếp phần cứng và các quyết định thiết kế phần mềm cốt lõi — đặc tả kiến trúc phần mềm</v>
       </c>
-      <c r="G11" t="str">
-        <v>Liệt kê chi tiết giá bán của các linh kiện điện tử trên thị trường — danh sách giá linh kiện</v>
-      </c>
       <c r="H11" t="str">
+        <v>Hướng dẫn người dùng cuối cách cắm sạc pin cho thiết bị di động — hướng dẫn sạc pin</v>
+      </c>
+      <c r="I11" t="str">
         <v>Ghi chép biên bản bàn giao thiết bị phần cứng cho khách hàng sử dụng — biên bản bàn giao thiết bị</v>
       </c>
-      <c r="I11" t="str">
-        <v>Hướng dẫn người dùng cuối cách cắm sạc pin cho thiết bị di động — hướng dẫn sạc pin</v>
-      </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
